--- a/rawresource/excels/player.xlsx
+++ b/rawresource/excels/player.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\MServer\rawresource\excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="500" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="hero" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="85">
   <si>
     <t>player/hero_conf</t>
   </si>
@@ -106,13 +111,16 @@
     <t>升级后英雄id</t>
   </si>
   <si>
-    <t>num</t>
+    <t>int</t>
   </si>
   <si>
     <t>str</t>
   </si>
   <si>
-    <t>json</t>
+    <t>double</t>
+  </si>
+  <si>
+    <t>array&lt;int&gt;</t>
   </si>
   <si>
     <t>sc</t>
@@ -199,7 +207,7 @@
     <t>战士</t>
   </si>
   <si>
-    <t>[10000,11000,12000,13000,14000]</t>
+    <t>{10000,11000,12000,13000,14000}</t>
   </si>
   <si>
     <t>0_HM</t>
@@ -223,7 +231,7 @@
     <t>新手邮件附件</t>
   </si>
   <si>
-    <t>lua</t>
+    <t>array&lt;array&lt;int&gt;&gt;</t>
   </si>
   <si>
     <t>s</t>
@@ -1478,6 +1486,7 @@
     <col min="18" max="18" width="11.75" customWidth="1"/>
     <col min="21" max="21" width="16.75" customWidth="1"/>
     <col min="22" max="22" width="12.6296296296296" customWidth="1"/>
+    <col min="23" max="23" width="14.5555555555556" customWidth="1"/>
     <col min="24" max="24" width="11.1296296296296" customWidth="1"/>
     <col min="25" max="25" width="11.6296296296296" customWidth="1"/>
   </cols>
@@ -1489,7 +1498,6 @@
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1"/>
       <c r="E1" t="s">
         <v>1</v>
       </c>
@@ -1627,10 +1635,10 @@
         <v>26</v>
       </c>
       <c r="V3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="W3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X3" t="s">
         <v>25</v>
@@ -1641,150 +1649,150 @@
     </row>
     <row r="4" spans="1:25">
       <c r="B4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="V4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:25">
       <c r="B5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1795,7 +1803,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6">
         <v>29</v>
@@ -1819,7 +1827,7 @@
         <v>400</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O6">
         <v>650</v>
@@ -1837,16 +1845,16 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="V6">
         <v>1</v>
       </c>
       <c r="W6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X6">
         <v>22</v>
@@ -1863,7 +1871,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>14</v>
@@ -1887,7 +1895,7 @@
         <v>800</v>
       </c>
       <c r="M7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O7">
         <v>230</v>
@@ -1905,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V7">
         <v>0.800000011920929</v>
@@ -1928,7 +1936,7 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8">
         <v>8</v>
@@ -1952,7 +1960,7 @@
         <v>400</v>
       </c>
       <c r="M8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O8">
         <v>200</v>
@@ -1970,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V8">
         <v>0.5</v>
@@ -1998,6 +2006,7 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="10.5925925925926" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="4" width="14.9166666666667" customWidth="1"/>
     <col min="5" max="5" width="37.0833333333333" customWidth="1"/>
   </cols>
@@ -2007,63 +2016,63 @@
         <v>-1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2090,11 +2099,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1"/>
+        <v>74</v>
+      </c>
       <c r="E1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2102,10 +2110,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2116,29 +2124,29 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2149,7 +2157,7 @@
         <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2160,7 +2168,7 @@
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2171,7 +2179,7 @@
         <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2182,7 +2190,7 @@
         <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2193,7 +2201,7 @@
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2204,7 +2212,7 @@
         <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2215,7 +2223,7 @@
         <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2226,7 +2234,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2237,7 +2245,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2248,7 +2256,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2259,7 +2267,7 @@
         <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2270,7 +2278,7 @@
         <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2281,7 +2289,7 @@
         <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2292,7 +2300,7 @@
         <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2303,7 +2311,7 @@
         <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2314,7 +2322,7 @@
         <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="2:4">
@@ -2325,7 +2333,7 @@
         <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="2:4">
@@ -2336,7 +2344,7 @@
         <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -2347,7 +2355,7 @@
         <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="2:4">
@@ -2358,7 +2366,7 @@
         <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="2:4">
@@ -2369,7 +2377,7 @@
         <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="2:4">
@@ -2380,7 +2388,7 @@
         <v>70</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="2:4">
@@ -2391,7 +2399,7 @@
         <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="2:4">
@@ -2402,7 +2410,7 @@
         <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="2:4">
@@ -2413,7 +2421,7 @@
         <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="2:4">
@@ -2424,7 +2432,7 @@
         <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="2:4">
@@ -2435,7 +2443,7 @@
         <v>70</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="2:4">
@@ -2446,7 +2454,7 @@
         <v>70</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="2:4">
@@ -2457,7 +2465,7 @@
         <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="2:4">
@@ -2468,7 +2476,7 @@
         <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="2:4">
@@ -2479,7 +2487,7 @@
         <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="2:4">
@@ -2490,7 +2498,7 @@
         <v>80</v>
       </c>
       <c r="D37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -2501,7 +2509,7 @@
         <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="2:4">
@@ -2512,7 +2520,7 @@
         <v>80</v>
       </c>
       <c r="D39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="2:4">
@@ -2523,7 +2531,7 @@
         <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="2:4">
@@ -2534,7 +2542,7 @@
         <v>80</v>
       </c>
       <c r="D41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="2:4">
@@ -2545,7 +2553,7 @@
         <v>80</v>
       </c>
       <c r="D42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="2:4">
@@ -2556,7 +2564,7 @@
         <v>80</v>
       </c>
       <c r="D43" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="2:4">
@@ -2567,7 +2575,7 @@
         <v>80</v>
       </c>
       <c r="D44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="2:4">
@@ -2578,7 +2586,7 @@
         <v>80</v>
       </c>
       <c r="D45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="2:4">
@@ -2589,7 +2597,7 @@
         <v>80</v>
       </c>
       <c r="D46" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="2:4">
@@ -2600,7 +2608,7 @@
         <v>80</v>
       </c>
       <c r="D47" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="2:4">
@@ -2611,7 +2619,7 @@
         <v>80</v>
       </c>
       <c r="D48" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="2:4">
@@ -2622,7 +2630,7 @@
         <v>80</v>
       </c>
       <c r="D49" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="2:4">
@@ -2633,7 +2641,7 @@
         <v>80</v>
       </c>
       <c r="D50" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="2:4">
@@ -2644,7 +2652,7 @@
         <v>80</v>
       </c>
       <c r="D51" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="2:4">
@@ -2655,7 +2663,7 @@
         <v>80</v>
       </c>
       <c r="D52" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="2:4">
@@ -2666,7 +2674,7 @@
         <v>80</v>
       </c>
       <c r="D53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="2:4">
@@ -2677,7 +2685,7 @@
         <v>80</v>
       </c>
       <c r="D54" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="2:4">
@@ -2688,7 +2696,7 @@
         <v>80</v>
       </c>
       <c r="D55" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="2:4">
@@ -2699,7 +2707,7 @@
         <v>80</v>
       </c>
       <c r="D56" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="2:4">
@@ -2710,7 +2718,7 @@
         <v>80</v>
       </c>
       <c r="D57" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="2:4">
@@ -2721,7 +2729,7 @@
         <v>80</v>
       </c>
       <c r="D58" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="2:4">
@@ -2732,7 +2740,7 @@
         <v>80</v>
       </c>
       <c r="D59" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="2:4">
@@ -2743,7 +2751,7 @@
         <v>80</v>
       </c>
       <c r="D60" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="2:4">
@@ -2754,7 +2762,7 @@
         <v>80</v>
       </c>
       <c r="D61" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="2:4">
@@ -2765,7 +2773,7 @@
         <v>80</v>
       </c>
       <c r="D62" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="2:4">
@@ -2776,7 +2784,7 @@
         <v>80</v>
       </c>
       <c r="D63" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="2:4">
@@ -2787,7 +2795,7 @@
         <v>80</v>
       </c>
       <c r="D64" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="2:4">
@@ -2798,7 +2806,7 @@
         <v>80</v>
       </c>
       <c r="D65" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="2:4">
@@ -2809,7 +2817,7 @@
         <v>80</v>
       </c>
       <c r="D66" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="2:4">
@@ -2820,7 +2828,7 @@
         <v>80</v>
       </c>
       <c r="D67" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="2:4">
@@ -2831,7 +2839,7 @@
         <v>80</v>
       </c>
       <c r="D68" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="2:4">
@@ -2842,7 +2850,7 @@
         <v>80</v>
       </c>
       <c r="D69" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70" spans="2:4">
@@ -2853,7 +2861,7 @@
         <v>80</v>
       </c>
       <c r="D70" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="2:4">
@@ -2864,7 +2872,7 @@
         <v>80</v>
       </c>
       <c r="D71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" spans="2:4">
@@ -2875,7 +2883,7 @@
         <v>80</v>
       </c>
       <c r="D72" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="2:4">
@@ -2886,7 +2894,7 @@
         <v>80</v>
       </c>
       <c r="D73" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="74" spans="2:4">
@@ -2897,7 +2905,7 @@
         <v>80</v>
       </c>
       <c r="D74" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="2:4">
@@ -2908,7 +2916,7 @@
         <v>80</v>
       </c>
       <c r="D75" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="2:4">
@@ -2919,7 +2927,7 @@
         <v>80</v>
       </c>
       <c r="D76" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="77" spans="2:4">
@@ -2930,7 +2938,7 @@
         <v>80</v>
       </c>
       <c r="D77" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" spans="2:4">
@@ -2941,7 +2949,7 @@
         <v>80</v>
       </c>
       <c r="D78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79" spans="2:4">
@@ -2952,7 +2960,7 @@
         <v>80</v>
       </c>
       <c r="D79" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80" spans="2:4">
@@ -2963,7 +2971,7 @@
         <v>80</v>
       </c>
       <c r="D80" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" spans="2:4">
@@ -2974,7 +2982,7 @@
         <v>80</v>
       </c>
       <c r="D81" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="2:4">
@@ -2985,7 +2993,7 @@
         <v>80</v>
       </c>
       <c r="D82" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="2:4">
@@ -2996,7 +3004,7 @@
         <v>80</v>
       </c>
       <c r="D83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84" spans="2:4">
@@ -3007,7 +3015,7 @@
         <v>80</v>
       </c>
       <c r="D84" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="2:4">
@@ -3018,7 +3026,7 @@
         <v>80</v>
       </c>
       <c r="D85" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86" spans="2:4">
@@ -3029,7 +3037,7 @@
         <v>80</v>
       </c>
       <c r="D86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" spans="2:4">
@@ -3040,7 +3048,7 @@
         <v>80</v>
       </c>
       <c r="D87" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88" spans="2:4">
@@ -3051,7 +3059,7 @@
         <v>80</v>
       </c>
       <c r="D88" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="89" spans="2:4">
@@ -3062,7 +3070,7 @@
         <v>80</v>
       </c>
       <c r="D89" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="90" spans="2:4">
@@ -3073,7 +3081,7 @@
         <v>80</v>
       </c>
       <c r="D90" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91" spans="2:4">
@@ -3084,7 +3092,7 @@
         <v>80</v>
       </c>
       <c r="D91" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="92" spans="2:4">
@@ -3095,7 +3103,7 @@
         <v>80</v>
       </c>
       <c r="D92" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="93" spans="2:4">
@@ -3106,7 +3114,7 @@
         <v>80</v>
       </c>
       <c r="D93" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="94" spans="2:4">
@@ -3117,7 +3125,7 @@
         <v>80</v>
       </c>
       <c r="D94" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="95" spans="2:4">
@@ -3128,7 +3136,7 @@
         <v>80</v>
       </c>
       <c r="D95" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96" spans="2:4">
@@ -3139,7 +3147,7 @@
         <v>80</v>
       </c>
       <c r="D96" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="97" spans="2:4">
@@ -3150,7 +3158,7 @@
         <v>80</v>
       </c>
       <c r="D97" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="98" spans="2:4">
@@ -3161,7 +3169,7 @@
         <v>80</v>
       </c>
       <c r="D98" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99" spans="2:4">
@@ -3172,7 +3180,7 @@
         <v>80</v>
       </c>
       <c r="D99" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="100" spans="2:4">
@@ -3183,7 +3191,7 @@
         <v>80</v>
       </c>
       <c r="D100" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="101" spans="2:4">
@@ -3194,7 +3202,7 @@
         <v>80</v>
       </c>
       <c r="D101" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" spans="2:4">
@@ -3205,7 +3213,7 @@
         <v>80</v>
       </c>
       <c r="D102" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="103" spans="2:4">
@@ -3216,7 +3224,7 @@
         <v>80</v>
       </c>
       <c r="D103" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="104" spans="2:4">
@@ -3227,7 +3235,7 @@
         <v>80</v>
       </c>
       <c r="D104" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
